--- a/grupos/1DM - Estadisticos 20241.xlsx
+++ b/grupos/1DM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -245,55 +245,52 @@
     <t>CORTES</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>ACATECATL</t>
+    <t>GAMBOA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
   </si>
   <si>
     <t>AREVALO</t>
   </si>
   <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
+    <t>ANGEL</t>
   </si>
   <si>
     <t>CANSECO</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
     <t>ALISON</t>
   </si>
   <si>
-    <t>NAARA SAFIR</t>
-  </si>
-  <si>
-    <t>MARIA NATHALIE</t>
+    <t>NATHAN KARLO</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>CRISTOFER FRANCISCO</t>
   </si>
   <si>
     <t>ALBA DANIELA</t>
   </si>
   <si>
-    <t>LUZ ELENA</t>
-  </si>
-  <si>
-    <t>NATHAN KARLO</t>
+    <t>KAREN ITAMAR</t>
   </si>
 </sst>
 </file>
@@ -839,28 +836,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -887,25 +884,25 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA4">
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>6</v>
       </c>
       <c r="AD4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE4">
         <v>9</v>
       </c>
       <c r="AF4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG4">
         <v>10</v>
@@ -940,28 +937,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1000,13 +997,13 @@
         <v>6</v>
       </c>
       <c r="AD5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5">
         <v>6</v>
       </c>
       <c r="AF5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG5">
         <v>10</v>
@@ -1041,28 +1038,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1101,7 +1098,7 @@
         <v>6</v>
       </c>
       <c r="AD6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE6">
         <v>7</v>
@@ -1142,28 +1139,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1243,28 +1240,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1297,13 +1294,13 @@
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC8">
         <v>10</v>
       </c>
       <c r="AD8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE8">
         <v>8</v>
@@ -1344,28 +1341,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1392,7 +1389,7 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA9">
         <v>6</v>
@@ -1404,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="AD9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE9">
         <v>6</v>
@@ -1445,28 +1442,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1499,7 +1496,7 @@
         <v>6</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>6</v>
@@ -1546,28 +1543,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1594,7 +1591,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>6</v>
@@ -1606,13 +1603,13 @@
         <v>6</v>
       </c>
       <c r="AD11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE11">
         <v>8</v>
       </c>
       <c r="AF11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG11">
         <v>10</v>
@@ -1647,28 +1644,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1707,13 +1704,13 @@
         <v>8</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE12">
         <v>9</v>
       </c>
       <c r="AF12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1748,28 +1745,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M13">
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1796,7 +1793,7 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -1808,13 +1805,13 @@
         <v>10</v>
       </c>
       <c r="AD13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE13">
         <v>8</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1849,28 +1846,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1903,13 +1900,13 @@
         <v>5</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC14">
         <v>6</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE14">
         <v>7</v>
@@ -1950,28 +1947,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1998,19 +1995,19 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA15">
         <v>6</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC15">
         <v>7</v>
       </c>
       <c r="AD15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE15">
         <v>6</v>
@@ -2051,28 +2048,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2117,7 +2114,7 @@
         <v>8</v>
       </c>
       <c r="AF16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG16">
         <v>10</v>
@@ -2152,28 +2149,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2206,7 +2203,7 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>10</v>
@@ -2218,7 +2215,7 @@
         <v>10</v>
       </c>
       <c r="AF17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2253,28 +2250,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2301,7 +2298,7 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2319,7 +2316,7 @@
         <v>6</v>
       </c>
       <c r="AF18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG18">
         <v>10</v>
@@ -2354,28 +2351,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2402,7 +2399,7 @@
         <v>-1</v>
       </c>
       <c r="Z19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA19">
         <v>6</v>
@@ -2414,7 +2411,7 @@
         <v>10</v>
       </c>
       <c r="AD19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE19">
         <v>6</v>
@@ -2455,28 +2452,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2509,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="AB20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC20">
         <v>6</v>
@@ -2521,7 +2518,7 @@
         <v>6</v>
       </c>
       <c r="AF20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2556,28 +2553,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2604,7 +2601,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21">
         <v>5</v>
@@ -2616,13 +2613,13 @@
         <v>6</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE21">
         <v>6</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2657,28 +2654,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2717,13 +2714,13 @@
         <v>6</v>
       </c>
       <c r="AD22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE22">
         <v>10</v>
       </c>
       <c r="AF22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2758,28 +2755,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2806,7 +2803,7 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2818,7 +2815,7 @@
         <v>8</v>
       </c>
       <c r="AD23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE23">
         <v>8</v>
@@ -2859,28 +2856,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2925,7 +2922,7 @@
         <v>6</v>
       </c>
       <c r="AF24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG24">
         <v>10</v>
@@ -2960,28 +2957,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3014,13 +3011,13 @@
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>6</v>
       </c>
       <c r="AD25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE25">
         <v>6</v>
@@ -3061,28 +3058,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3109,7 +3106,7 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>7</v>
@@ -3127,7 +3124,7 @@
         <v>7</v>
       </c>
       <c r="AF26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG26">
         <v>10</v>
@@ -3162,28 +3159,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3222,13 +3219,13 @@
         <v>6</v>
       </c>
       <c r="AD27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE27">
         <v>6</v>
       </c>
       <c r="AF27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3263,28 +3260,28 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3311,19 +3308,19 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA28">
         <v>5</v>
       </c>
       <c r="AB28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC28">
         <v>7</v>
       </c>
       <c r="AD28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE28">
         <v>6</v>
@@ -3364,28 +3361,28 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>-1</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3412,25 +3409,25 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA29">
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC29">
         <v>10</v>
       </c>
       <c r="AD29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE29">
         <v>8</v>
       </c>
       <c r="AF29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3465,28 +3462,28 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>-1</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3519,13 +3516,13 @@
         <v>6</v>
       </c>
       <c r="AB30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC30">
         <v>6</v>
       </c>
       <c r="AD30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE30">
         <v>8</v>
@@ -3566,28 +3563,28 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>-1</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3626,13 +3623,13 @@
         <v>8</v>
       </c>
       <c r="AD31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE31">
         <v>8</v>
       </c>
       <c r="AF31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3667,28 +3664,28 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
         <v>-1</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3715,7 +3712,7 @@
         <v>-1</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA32">
         <v>7</v>
@@ -3727,13 +3724,13 @@
         <v>10</v>
       </c>
       <c r="AD32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE32">
         <v>8</v>
       </c>
       <c r="AF32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3768,28 +3765,28 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>-1</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3816,7 +3813,7 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA33">
         <v>6</v>
@@ -3828,7 +3825,7 @@
         <v>10</v>
       </c>
       <c r="AD33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE33">
         <v>7</v>
@@ -3869,28 +3866,28 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>-1</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3923,7 +3920,7 @@
         <v>6</v>
       </c>
       <c r="AB34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC34">
         <v>7</v>
@@ -3935,7 +3932,7 @@
         <v>6</v>
       </c>
       <c r="AF34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG34">
         <v>10</v>
@@ -3970,28 +3967,28 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
         <v>-1</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4030,13 +4027,13 @@
         <v>8</v>
       </c>
       <c r="AD35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE35">
         <v>10</v>
       </c>
       <c r="AF35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4071,28 +4068,28 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
         <v>-1</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4119,7 +4116,7 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA36">
         <v>7</v>
@@ -4172,28 +4169,28 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>-1</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4226,13 +4223,13 @@
         <v>6</v>
       </c>
       <c r="AB37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC37">
         <v>10</v>
       </c>
       <c r="AD37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE37">
         <v>6</v>
@@ -4273,28 +4270,28 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M38">
         <v>-1</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -4321,13 +4318,13 @@
         <v>-1</v>
       </c>
       <c r="Z38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA38">
         <v>5</v>
       </c>
       <c r="AB38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC38">
         <v>6</v>
@@ -4339,7 +4336,7 @@
         <v>6</v>
       </c>
       <c r="AF38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4374,28 +4371,28 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
         <v>-1</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -4434,13 +4431,13 @@
         <v>7</v>
       </c>
       <c r="AD39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE39">
         <v>10</v>
       </c>
       <c r="AF39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4692,13 +4689,13 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O5">
         <v>100</v>
@@ -4716,13 +4713,13 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U5">
         <v>100</v>
       </c>
       <c r="V5">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W5">
         <v>100</v>
@@ -4923,13 +4920,13 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -4947,13 +4944,13 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U8">
         <v>100</v>
       </c>
       <c r="V8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W8">
         <v>100</v>
@@ -5077,13 +5074,13 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -5101,13 +5098,13 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>95.8</v>
+        <v>93.2</v>
       </c>
       <c r="U10">
         <v>100</v>
       </c>
       <c r="V10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W10">
         <v>100</v>
@@ -5154,13 +5151,13 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M11">
         <v>100</v>
       </c>
       <c r="N11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -5178,13 +5175,13 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U11">
         <v>100</v>
       </c>
       <c r="V11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W11">
         <v>100</v>
@@ -5237,7 +5234,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -5261,7 +5258,7 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W12">
         <v>100</v>
@@ -5770,7 +5767,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -5794,7 +5791,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5847,19 +5844,19 @@
         <v>80</v>
       </c>
       <c r="L20">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -5871,19 +5868,19 @@
         <v>80</v>
       </c>
       <c r="T20">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U20">
         <v>100</v>
       </c>
       <c r="V20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="W20">
         <v>100</v>
       </c>
       <c r="X20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -5930,7 +5927,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -5954,7 +5951,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W21">
         <v>100</v>
@@ -6001,7 +5998,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -6025,7 +6022,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -6078,7 +6075,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -6102,7 +6099,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -6155,7 +6152,7 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -6179,7 +6176,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -6232,7 +6229,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -6256,7 +6253,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -6309,7 +6306,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -6333,7 +6330,7 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="U26">
         <v>100</v>
@@ -6386,7 +6383,7 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -6410,7 +6407,7 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -6463,7 +6460,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -6487,7 +6484,7 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U28">
         <v>100</v>
@@ -6694,7 +6691,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -6718,7 +6715,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7002,7 +6999,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M35">
         <v>100</v>
@@ -7026,7 +7023,7 @@
         <v>100</v>
       </c>
       <c r="T35">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U35">
         <v>100</v>
@@ -7079,7 +7076,7 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="M36">
         <v>100</v>
@@ -7103,7 +7100,7 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="U36">
         <v>100</v>
@@ -7233,7 +7230,7 @@
         <v>100</v>
       </c>
       <c r="L38">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="M38">
         <v>100</v>
@@ -7257,7 +7254,7 @@
         <v>100</v>
       </c>
       <c r="T38">
-        <v>95.8</v>
+        <v>95.5</v>
       </c>
       <c r="U38">
         <v>100</v>
@@ -7447,19 +7444,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2">
-        <v>83.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7479,19 +7476,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>83.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>16.7</v>
+        <v>5.6</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7555,7 +7552,7 @@
         <v>2.8</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7701,7 +7698,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7742,7 +7739,7 @@
         <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7765,7 +7762,7 @@
         <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -7779,7 +7776,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920162</v>
+        <v>24330051920216</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
@@ -7788,7 +7785,7 @@
         <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7802,7 +7799,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920162</v>
+        <v>24330051920216</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
@@ -7811,13 +7808,13 @@
         <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7825,7 +7822,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920151</v>
+        <v>24330051920359</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
@@ -7834,13 +7831,13 @@
         <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7848,16 +7845,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920358</v>
+        <v>24330051920359</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -7871,22 +7868,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920167</v>
+        <v>24330051920163</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7894,24 +7891,70 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920216</v>
+        <v>24330051920163</v>
       </c>
       <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>24330051920358</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920195</v>
+      </c>
+      <c r="B11" t="s">
         <v>79</v>
       </c>
-      <c r="C9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
         <v>62</v>
       </c>
-      <c r="G9">
+      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20241.xlsx
+++ b/grupos/1DM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -212,6 +212,12 @@
     <t>Santiago Hernández Mariana</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
@@ -221,12 +227,6 @@
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
@@ -260,6 +260,9 @@
     <t>ANGEL</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CANSECO</t>
   </si>
   <si>
@@ -275,6 +278,9 @@
     <t>MARIA</t>
   </si>
   <si>
+    <t>MOCTEZUMA</t>
+  </si>
+  <si>
     <t>ALISON</t>
   </si>
   <si>
@@ -291,6 +297,9 @@
   </si>
   <si>
     <t>KAREN ITAMAR</t>
+  </si>
+  <si>
+    <t>ZURY DALAY</t>
   </si>
 </sst>
 </file>
@@ -839,19 +848,19 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>9</v>
@@ -887,19 +896,19 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD4">
         <v>7</v>
       </c>
       <c r="AE4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF4">
         <v>7</v>
@@ -940,19 +949,19 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>7</v>
@@ -994,7 +1003,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD5">
         <v>6</v>
@@ -1041,19 +1050,19 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>7</v>
@@ -1089,19 +1098,19 @@
         <v>7</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>9</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD6">
         <v>7</v>
       </c>
       <c r="AE6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF6">
         <v>8</v>
@@ -1142,19 +1151,19 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -1196,13 +1205,13 @@
         <v>9</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD7">
         <v>7</v>
       </c>
       <c r="AE7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF7">
         <v>6</v>
@@ -1243,19 +1252,19 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>5</v>
@@ -1303,7 +1312,7 @@
         <v>8</v>
       </c>
       <c r="AE8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF8">
         <v>5</v>
@@ -1344,19 +1353,19 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -1398,13 +1407,13 @@
         <v>8</v>
       </c>
       <c r="AC9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD9">
         <v>7</v>
       </c>
       <c r="AE9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF9">
         <v>7</v>
@@ -1445,19 +1454,19 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
         <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>6</v>
@@ -1493,13 +1502,13 @@
         <v>10</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD10">
         <v>7</v>
@@ -1546,19 +1555,19 @@
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -1600,7 +1609,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD11">
         <v>7</v>
@@ -1647,19 +1656,19 @@
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>6</v>
@@ -1748,19 +1757,19 @@
         <v>9</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>10</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>6</v>
@@ -1796,7 +1805,7 @@
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1849,19 +1858,19 @@
         <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -1903,7 +1912,7 @@
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>7</v>
@@ -1950,19 +1959,19 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -2004,13 +2013,13 @@
         <v>7</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD15">
         <v>7</v>
       </c>
       <c r="AE15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF15">
         <v>7</v>
@@ -2051,19 +2060,19 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
         <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>10</v>
@@ -2105,7 +2114,7 @@
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD16">
         <v>6</v>
@@ -2152,19 +2161,19 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -2200,7 +2209,7 @@
         <v>9</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>10</v>
@@ -2212,7 +2221,7 @@
         <v>8</v>
       </c>
       <c r="AE17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF17">
         <v>7</v>
@@ -2253,19 +2262,19 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>7</v>
@@ -2307,7 +2316,7 @@
         <v>8</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD18">
         <v>6</v>
@@ -2354,19 +2363,19 @@
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
         <v>9</v>
@@ -2402,19 +2411,19 @@
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD19">
         <v>6</v>
       </c>
       <c r="AE19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF19">
         <v>9</v>
@@ -2455,19 +2464,19 @@
         <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>5</v>
@@ -2509,13 +2518,13 @@
         <v>6</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD20">
         <v>5</v>
       </c>
       <c r="AE20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF20">
         <v>7</v>
@@ -2556,19 +2565,19 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>5</v>
@@ -2604,19 +2613,19 @@
         <v>9</v>
       </c>
       <c r="AA21">
+        <v>6</v>
+      </c>
+      <c r="AB21">
+        <v>8</v>
+      </c>
+      <c r="AC21">
         <v>5</v>
       </c>
-      <c r="AB21">
-        <v>8</v>
-      </c>
-      <c r="AC21">
-        <v>6</v>
-      </c>
       <c r="AD21">
         <v>7</v>
       </c>
       <c r="AE21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF21">
         <v>5</v>
@@ -2657,19 +2666,19 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P22">
         <v>10</v>
@@ -2705,19 +2714,19 @@
         <v>10</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB22">
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD22">
         <v>9</v>
       </c>
       <c r="AE22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF22">
         <v>9</v>
@@ -2758,19 +2767,19 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>8</v>
@@ -2806,13 +2815,13 @@
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>9</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD23">
         <v>8</v>
@@ -2859,19 +2868,19 @@
         <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
         <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>5</v>
@@ -2913,13 +2922,13 @@
         <v>8</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD24">
         <v>6</v>
       </c>
       <c r="AE24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF24">
         <v>7</v>
@@ -2960,19 +2969,19 @@
         <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N25">
         <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
         <v>5</v>
@@ -3014,13 +3023,13 @@
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD25">
         <v>6</v>
       </c>
       <c r="AE25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF25">
         <v>5</v>
@@ -3061,19 +3070,19 @@
         <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
         <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>9</v>
@@ -3109,13 +3118,13 @@
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>9</v>
       </c>
       <c r="AC26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD26">
         <v>7</v>
@@ -3162,19 +3171,19 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>8</v>
@@ -3210,19 +3219,19 @@
         <v>10</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>10</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD27">
         <v>8</v>
       </c>
       <c r="AE27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF27">
         <v>8</v>
@@ -3263,19 +3272,19 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>5</v>
@@ -3317,7 +3326,7 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD28">
         <v>6</v>
@@ -3364,19 +3373,19 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>10</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
         <v>6</v>
@@ -3424,7 +3433,7 @@
         <v>7</v>
       </c>
       <c r="AE29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF29">
         <v>8</v>
@@ -3465,19 +3474,19 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>7</v>
@@ -3519,13 +3528,13 @@
         <v>10</v>
       </c>
       <c r="AC30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD30">
         <v>8</v>
       </c>
       <c r="AE30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF30">
         <v>7</v>
@@ -3566,19 +3575,19 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>9</v>
@@ -3667,19 +3676,19 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
         <v>9</v>
@@ -3727,7 +3736,7 @@
         <v>8</v>
       </c>
       <c r="AE32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF32">
         <v>9</v>
@@ -3768,19 +3777,19 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
         <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>6</v>
@@ -3822,7 +3831,7 @@
         <v>8</v>
       </c>
       <c r="AC33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD33">
         <v>8</v>
@@ -3869,19 +3878,19 @@
         <v>10</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>9</v>
@@ -3917,19 +3926,19 @@
         <v>10</v>
       </c>
       <c r="AA34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB34">
         <v>10</v>
       </c>
       <c r="AC34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AD34">
         <v>8</v>
       </c>
       <c r="AE34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF34">
         <v>9</v>
@@ -3970,19 +3979,19 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
         <v>10</v>
@@ -4030,7 +4039,7 @@
         <v>8</v>
       </c>
       <c r="AE35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF35">
         <v>10</v>
@@ -4071,19 +4080,19 @@
         <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>8</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>8</v>
@@ -4125,13 +4134,13 @@
         <v>9</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD36">
         <v>8</v>
       </c>
       <c r="AE36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF36">
         <v>9</v>
@@ -4172,19 +4181,19 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
         <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
         <v>8</v>
@@ -4220,7 +4229,7 @@
         <v>10</v>
       </c>
       <c r="AA37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB37">
         <v>8</v>
@@ -4232,7 +4241,7 @@
         <v>7</v>
       </c>
       <c r="AE37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF37">
         <v>8</v>
@@ -4273,19 +4282,19 @@
         <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L38">
         <v>5</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>6</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P38">
         <v>6</v>
@@ -4327,13 +4336,13 @@
         <v>5</v>
       </c>
       <c r="AC38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD38">
         <v>5</v>
       </c>
       <c r="AE38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF38">
         <v>7</v>
@@ -4374,19 +4383,19 @@
         <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
         <v>9</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>9</v>
@@ -4428,13 +4437,13 @@
         <v>10</v>
       </c>
       <c r="AC39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD39">
         <v>7</v>
       </c>
       <c r="AE39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF39">
         <v>9</v>
@@ -4994,7 +5003,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -5018,7 +5027,7 @@
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T9">
         <v>100</v>
@@ -5071,7 +5080,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L10">
         <v>93.2</v>
@@ -5095,7 +5104,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T10">
         <v>93.2</v>
@@ -5302,7 +5311,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -5326,7 +5335,7 @@
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T13">
         <v>100</v>
@@ -5841,19 +5850,19 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L20">
         <v>95.5</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N20">
         <v>50</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="P20">
         <v>50</v>
@@ -5865,19 +5874,19 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="T20">
         <v>95.5</v>
       </c>
       <c r="U20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="V20">
         <v>50</v>
       </c>
       <c r="W20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="X20">
         <v>50</v>
@@ -5918,7 +5927,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -5942,7 +5951,7 @@
         <v>100</v>
       </c>
       <c r="S21">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -6765,7 +6774,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -6789,7 +6798,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -7424,7 +7433,7 @@
         <v>19.4</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7467,7 +7476,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -7476,19 +7485,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>94.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="G4" s="2">
-        <v>5.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7499,7 +7508,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -7508,19 +7517,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>97.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7531,7 +7540,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -7540,19 +7549,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>97.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7563,7 +7572,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -7572,19 +7581,19 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7595,7 +7604,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
@@ -7604,19 +7613,19 @@
         <v>36</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="H8">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7698,7 +7707,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7736,10 +7745,10 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7759,10 +7768,10 @@
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -7782,16 +7791,16 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7805,10 +7814,10 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -7828,10 +7837,10 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -7851,10 +7860,10 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -7874,10 +7883,10 @@
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -7897,10 +7906,10 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -7923,7 +7932,7 @@
         <v>76</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -7943,10 +7952,10 @@
         <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -7955,6 +7964,29 @@
         <v>62</v>
       </c>
       <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920367</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20241.xlsx
+++ b/grupos/1DM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="97">
   <si>
     <t>Materia</t>
   </si>
@@ -242,6 +242,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>CORTES</t>
   </si>
   <si>
@@ -263,6 +266,9 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>CANSECO</t>
   </si>
   <si>
@@ -279,6 +285,9 @@
   </si>
   <si>
     <t>MOCTEZUMA</t>
+  </si>
+  <si>
+    <t>NAARA SAFIR</t>
   </si>
   <si>
     <t>ALISON</t>
@@ -847,13 +856,13 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -936,13 +945,13 @@
         <v>7</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1025,13 +1034,13 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1114,13 +1123,13 @@
         <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1135,7 +1144,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1203,13 +1212,13 @@
         <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1292,13 +1301,13 @@
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1381,13 +1390,13 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1470,13 +1479,13 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1491,13 +1500,13 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>6</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <v>7</v>
@@ -1559,13 +1568,13 @@
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1586,7 +1595,7 @@
         <v>7</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z12">
         <v>8</v>
@@ -1648,13 +1657,13 @@
         <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1737,13 +1746,13 @@
         <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1826,13 +1835,13 @@
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1847,7 +1856,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1915,13 +1924,13 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2004,13 +2013,13 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2093,13 +2102,13 @@
         <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2182,13 +2191,13 @@
         <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2271,13 +2280,13 @@
         <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2298,7 +2307,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <v>5</v>
@@ -2360,13 +2369,13 @@
         <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2387,7 +2396,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2449,13 +2458,13 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2538,13 +2547,13 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2559,7 +2568,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2627,13 +2636,13 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2716,13 +2725,13 @@
         <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2805,13 +2814,13 @@
         <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2894,13 +2903,13 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2983,13 +2992,13 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3072,13 +3081,13 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3093,13 +3102,13 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <v>10</v>
@@ -3161,13 +3170,13 @@
         <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3182,7 +3191,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -3250,13 +3259,13 @@
         <v>9</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3339,13 +3348,13 @@
         <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3366,7 +3375,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z32">
         <v>10</v>
@@ -3428,13 +3437,13 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3517,13 +3526,13 @@
         <v>9</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3606,13 +3615,13 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3695,13 +3704,13 @@
         <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3784,13 +3793,13 @@
         <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3811,7 +3820,7 @@
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z37">
         <v>10</v>
@@ -3873,13 +3882,13 @@
         <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3900,7 +3909,7 @@
         <v>5</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z38">
         <v>5</v>
@@ -3962,13 +3971,13 @@
         <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -4247,7 +4256,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4451,7 +4460,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4587,7 +4596,7 @@
         <v>90</v>
       </c>
       <c r="R10">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -4655,7 +4664,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -5199,7 +5208,7 @@
         <v>100</v>
       </c>
       <c r="R19">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5267,7 +5276,7 @@
         <v>40</v>
       </c>
       <c r="R20">
-        <v>95.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="S20">
         <v>50</v>
@@ -5403,7 +5412,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5471,7 +5480,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5539,7 +5548,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5607,7 +5616,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -5675,7 +5684,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5743,7 +5752,7 @@
         <v>100</v>
       </c>
       <c r="R27">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5811,7 +5820,7 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -6015,7 +6024,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -6287,7 +6296,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -6355,7 +6364,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6491,7 +6500,7 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -6809,7 +6818,7 @@
         <v>2.8</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6841,7 +6850,7 @@
         <v>2.8</v>
       </c>
       <c r="H8">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6911,7 +6920,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6943,16 +6952,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920160</v>
+        <v>24330051920162</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6966,22 +6975,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920160</v>
+        <v>24330051920162</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6989,22 +6998,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920216</v>
+        <v>24330051920162</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
         <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7012,22 +7021,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920216</v>
+        <v>24330051920162</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
         <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7035,16 +7044,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920359</v>
+        <v>24330051920160</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
         <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -7058,16 +7067,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920359</v>
+        <v>24330051920160</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -7081,22 +7090,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920163</v>
+        <v>24330051920216</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7104,16 +7113,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920163</v>
+        <v>24330051920216</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
         <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -7127,22 +7136,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920358</v>
+        <v>24330051920359</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7150,10 +7159,10 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920195</v>
+        <v>24330051920359</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
@@ -7162,10 +7171,10 @@
         <v>92</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7173,10 +7182,10 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920367</v>
+        <v>24330051920163</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
         <v>86</v>
@@ -7191,6 +7200,98 @@
         <v>62</v>
       </c>
       <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920163</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920358</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920195</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920367</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1DM - Estadisticos 20241.xlsx
+++ b/grupos/1DM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="77">
   <si>
     <t>Materia</t>
   </si>
@@ -206,24 +206,24 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Santiago Hernández Mariana</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Santiago Hernández Mariana</t>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -242,73 +242,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GAMBOA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>AREVALO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>MOCTEZUMA</t>
-  </si>
-  <si>
-    <t>NAARA SAFIR</t>
-  </si>
-  <si>
-    <t>ALISON</t>
-  </si>
-  <si>
-    <t>NATHAN KARLO</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
     <t>CRISTOFER FRANCISCO</t>
-  </si>
-  <si>
-    <t>ALBA DANIELA</t>
-  </si>
-  <si>
-    <t>KAREN ITAMAR</t>
-  </si>
-  <si>
-    <t>ZURY DALAY</t>
   </si>
 </sst>
 </file>
@@ -859,22 +799,22 @@
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -895,7 +835,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -948,28 +888,28 @@
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -981,7 +921,7 @@
         <v>6</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>6</v>
@@ -1037,28 +977,28 @@
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>7</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1067,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="AA6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>8</v>
@@ -1126,22 +1066,22 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1153,13 +1093,13 @@
         <v>9</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>7</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC7">
         <v>6</v>
@@ -1215,43 +1155,43 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1304,22 +1244,22 @@
         <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1337,10 +1277,10 @@
         <v>7</v>
       </c>
       <c r="AB9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1393,28 +1333,28 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1429,7 +1369,7 @@
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1482,22 +1422,22 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1512,13 +1452,13 @@
         <v>7</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>8</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1571,28 +1511,28 @@
         <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1601,13 +1541,13 @@
         <v>8</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1660,34 +1600,34 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1696,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1749,28 +1689,28 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1779,13 +1719,13 @@
         <v>8</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1838,22 +1778,22 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1868,10 +1808,10 @@
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>7</v>
@@ -1927,22 +1867,22 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1954,7 +1894,7 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>6</v>
@@ -1963,7 +1903,7 @@
         <v>8</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2016,22 +1956,22 @@
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2043,16 +1983,16 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB17">
         <v>9</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2105,40 +2045,40 @@
         <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>8</v>
       </c>
       <c r="Z18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC18">
         <v>7</v>
@@ -2194,22 +2134,22 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2224,13 +2164,13 @@
         <v>9</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2283,22 +2223,22 @@
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <v>5</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2319,7 +2259,7 @@
         <v>5</v>
       </c>
       <c r="AC20">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2372,22 +2312,22 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2399,7 +2339,7 @@
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>7</v>
@@ -2408,7 +2348,7 @@
         <v>7</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2461,28 +2401,28 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>10</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>10</v>
@@ -2550,22 +2490,22 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>8</v>
@@ -2639,22 +2579,22 @@
         <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
         <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2666,10 +2606,10 @@
         <v>8</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>7</v>
@@ -2728,28 +2668,28 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>7</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2764,7 +2704,7 @@
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2817,28 +2757,28 @@
         <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2847,13 +2787,13 @@
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2906,28 +2846,28 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
         <v>10</v>
@@ -2936,10 +2876,10 @@
         <v>8</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>8</v>
@@ -2995,34 +2935,34 @@
         <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>6</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>7</v>
       </c>
       <c r="Z28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>6</v>
@@ -3084,22 +3024,22 @@
         <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3111,10 +3051,10 @@
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>7</v>
@@ -3173,28 +3113,28 @@
         <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>9</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -3203,13 +3143,13 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC30">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3262,22 +3202,22 @@
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3351,43 +3291,43 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>10</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>9</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB32">
         <v>9</v>
       </c>
       <c r="AC32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:29">
@@ -3440,22 +3380,22 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3467,7 +3407,7 @@
         <v>8</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3476,7 +3416,7 @@
         <v>7</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3529,28 +3469,28 @@
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>10</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>10</v>
@@ -3559,10 +3499,10 @@
         <v>9</v>
       </c>
       <c r="AA34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC34">
         <v>9</v>
@@ -3618,28 +3558,28 @@
         <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>10</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -3648,13 +3588,13 @@
         <v>8</v>
       </c>
       <c r="AA35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB35">
         <v>9</v>
       </c>
       <c r="AC35">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:29">
@@ -3707,28 +3647,28 @@
         <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
         <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W36">
         <v>10</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3740,7 +3680,7 @@
         <v>8</v>
       </c>
       <c r="AB36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC36">
         <v>9</v>
@@ -3796,40 +3736,40 @@
         <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>10</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y37">
         <v>9</v>
       </c>
       <c r="Z37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA37">
         <v>7</v>
       </c>
       <c r="AB37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC37">
         <v>8</v>
@@ -3885,40 +3825,40 @@
         <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>6</v>
       </c>
       <c r="X38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>7</v>
       </c>
       <c r="Z38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC38">
         <v>7</v>
@@ -3974,28 +3914,28 @@
         <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
         <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W39">
         <v>10</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -4010,7 +3950,7 @@
         <v>9</v>
       </c>
       <c r="AC39">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4262,7 +4202,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -4466,7 +4406,7 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U8">
         <v>100</v>
@@ -4525,7 +4465,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4593,16 +4533,16 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R10">
         <v>95.3</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T10">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -4670,7 +4610,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4738,7 +4678,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4797,7 +4737,7 @@
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4871,7 +4811,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -5273,22 +5213,22 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="R20">
         <v>65.59999999999999</v>
       </c>
       <c r="S20">
-        <v>50</v>
+        <v>60.4</v>
       </c>
       <c r="T20">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="U20">
-        <v>50</v>
+        <v>35.3</v>
       </c>
       <c r="V20">
-        <v>50</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5341,7 +5281,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5350,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U21">
         <v>100</v>
@@ -5619,7 +5559,7 @@
         <v>95.3</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T25">
         <v>100</v>
@@ -6089,7 +6029,7 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -6163,7 +6103,7 @@
         <v>100</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T33">
         <v>100</v>
@@ -6367,7 +6307,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T36">
         <v>100</v>
@@ -6571,7 +6511,7 @@
         <v>100</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T39">
         <v>100</v>
@@ -6637,7 +6577,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -6646,19 +6586,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>80.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>19.4</v>
+        <v>5.6</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6669,7 +6609,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -6678,19 +6618,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>86.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="G3" s="2">
-        <v>13.9</v>
+        <v>2.8</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6701,7 +6641,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -6710,19 +6650,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>91.7</v>
+        <v>97.2</v>
       </c>
       <c r="G4" s="2">
-        <v>8.300000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6742,19 +6682,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>94.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="G5" s="2">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6765,7 +6705,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -6774,19 +6714,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>94.40000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="G6" s="2">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6797,7 +6737,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -6818,7 +6758,7 @@
         <v>2.8</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6920,7 +6860,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6952,346 +6892,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920162</v>
+        <v>24330051920163</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
         <v>62</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>24330051920162</v>
-      </c>
-      <c r="B3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>24330051920162</v>
-      </c>
-      <c r="B4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920162</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920160</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920160</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920216</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>24330051920216</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>24330051920359</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920359</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>92</v>
-      </c>
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920163</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920163</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920358</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" t="s">
-        <v>94</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920195</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920367</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>96</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>
